--- a/ig/nr-review/StructureDefinition-as-address-extended.xlsx
+++ b/ig/nr-review/StructureDefinition-as-address-extended.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-16T08:18:01+00:00</t>
+    <t>2023-05-16T09:18:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
